--- a/Plantillas_carga_masiva/Panama/Estructura_Cargue_Masivo_Instrumentos.xlsx
+++ b/Plantillas_carga_masiva/Panama/Estructura_Cargue_Masivo_Instrumentos.xlsx
@@ -138,7 +138,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARGA829588</t>
+          <t xml:space="preserve">CARGA114142</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Plantillas_carga_masiva/Panama/Estructura_Cargue_Masivo_Instrumentos.xlsx
+++ b/Plantillas_carga_masiva/Panama/Estructura_Cargue_Masivo_Instrumentos.xlsx
@@ -138,7 +138,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARGA114142</t>
+          <t xml:space="preserve">CARGA617126</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Plantillas_carga_masiva/Panama/Estructura_Cargue_Masivo_Instrumentos.xlsx
+++ b/Plantillas_carga_masiva/Panama/Estructura_Cargue_Masivo_Instrumentos.xlsx
@@ -138,7 +138,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARGA617126</t>
+          <t xml:space="preserve">CARGA765268</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
